--- a/光伏配储项目/电价数据/2026/从化站.xlsx
+++ b/光伏配储项目/电价数据/2026/从化站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5127</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7480599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57664</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58438</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50636</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45474</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11901</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09733</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10685</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09589</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08551</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.12448</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.11226</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.08158</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09029999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.08829000000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.05709</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14419</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21308</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.12469</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25838</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20074</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5561</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.49518</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67924</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5674400000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56576</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60346</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7988</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6266699999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63201</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73838</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.92832</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65924</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58297</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.72357</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47448</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60358</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42598</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6916599999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.00299</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63761</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.55141</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6670199999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49372</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51744</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50491</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46889</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48406</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55153</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.49113</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48183</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74954</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.96815</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5404500000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.6355700000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.59721</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.51702</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.53224</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.70602</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.56577</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48122</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.72968</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5139900000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43973</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.59024</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48522</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49308</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5882200000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6715099999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6329400000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7193200000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76595</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47094</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.4659700000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43554</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50978</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42928</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43947</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25249</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5252599999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8536699999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5694199999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.54874</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.44566</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.51359</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.51186</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45883</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45149</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52442</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60876</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5767100000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59614</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48195</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44725</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47922</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12553</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24175</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19896</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20111</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56116</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21774</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.23112</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60407</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.24147</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48004</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16488</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49705</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31644</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21822</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22728</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21908</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2131</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.22403</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.22002</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19767</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02869</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09906000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.17401</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.12396</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.11306</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.08470999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04241</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.18919</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03814</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.18874</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.18466</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.21641</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00205</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.01443</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03392</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09584999999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35051</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65237</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44346</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04345</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.02956</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.06783</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.009789999999999998</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.09766</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.09598999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33515</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31693</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15857</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41537</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15652</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91415</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86266</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29612</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88732</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63158</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18691</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86851</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53232</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33066</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03279</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5306000000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7908200000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52858</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77281</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7774099999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87675</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87378</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49299</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39969</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2068</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6216499999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53827</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49763</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43323</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5844400000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5951900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60023</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6884199999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57926</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8704400000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62305</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86488</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82926</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8613099999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.58877</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26813</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35307</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91762</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46216</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16708</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27716</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.1927</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44113</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5928099999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88897</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.49196</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.15858</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6992699999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79003</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6626299999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49879</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42207</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49411</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55304</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26143</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25522</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56902</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46093</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46311</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.46865</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32275</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22718</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14609</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15341</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14141</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13691</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24901</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13761</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25583</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13837</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.10943</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10874</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10805</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12964</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13668</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44176</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34776</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53551</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46645</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20269</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2436</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25925</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3595</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42501</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51903</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.58687</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.25027</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.6728</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.49356</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22273</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32261</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.67716</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.17831</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>1.17129</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>1.16317</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>1.16921</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>1.16436</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>1.17477</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.69202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>1.59015</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.87425</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>1.02407</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34951</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.5744600000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.81713</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77015</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34425</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14847</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19976</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25391</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25536</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.8145399999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.04056</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.99803</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.00598</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8863099999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.21247</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48769</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.21453</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.7216399999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.62634</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.79539</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.58572</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.70301</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35986</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5270199999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47957</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49869</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49391</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43818</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43099</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.63559</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43612</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49202</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.90219</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.9434400000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.09115</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.11237</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.32537</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80621</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58233</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83143</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7701</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67214</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48171</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47616</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46891</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5511900000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19711</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10797</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17999</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40881</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36514</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2463</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13951</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24316</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16929</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18744</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25809</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23183</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28322</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34899</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14851</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03954999999999999</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01481</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04266</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04854</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04819</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02436</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02896</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03724</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01728</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03587</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20313</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.34232</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.82045</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.68641</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.85862</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.96062</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87674</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83585</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11651</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.08878</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.02475</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00213</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00149</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06016</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25486</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32258</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.21355</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.46632</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.50252</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5228700000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14097</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33031</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46426</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.48896</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47073</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47533</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.47261</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.59962</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45514</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36701</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47552</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43662</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50336</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5777899999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58466</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.48676</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.61753</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6676299999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49731</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.53555</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.65887</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8270700000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7273999999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.55525</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53692</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.51197</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37133</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.15454</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06589</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.16829</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.2348</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20915</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15575</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26139</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15484</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06792000000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08131999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22767</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08398</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05766</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.2127</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16418</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.18916</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46104</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37663</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.00497</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56153</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49865</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.22699</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.23247</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.24059</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.47466</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.46812</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.10721</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.49191</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.51574</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36598</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17307</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14288</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.15562</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.15484</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.22552</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22676</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.19733</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22192</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15134</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15252</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19372</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14213</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2779700000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.24469</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38979</v>
       </c>
     </row>
   </sheetData>
